--- a/3курс/Лабораторные/Архитектура ЭВМ/1/сдвигатель_полная схема.xlsx
+++ b/3курс/Лабораторные/Архитектура ЭВМ/1/сдвигатель_полная схема.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repos\Облако\ВУЗ\3курс\Лабораторные\Архитектура ЭВМ\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C91150C-1FDB-42E5-B602-8C804D49D38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41712FA-081E-448A-9E00-7CA7963176EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B04BFBAC-6633-47BD-86B3-35EFB2D27481}"/>
   </bookViews>
@@ -33,32 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -271,8 +245,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="889426" y="2672226"/>
-          <a:ext cx="13777325" cy="27797074"/>
+          <a:off x="889426" y="2689619"/>
+          <a:ext cx="13801345" cy="27949889"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -309,6 +283,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
           <a:endParaRPr lang="ru-RU" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -316,70 +294,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -699,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD3A7FC-84A9-4A37-90EA-31D16F697D22}">
-  <dimension ref="A3:AV143"/>
+  <dimension ref="B14:AF143"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.75" style="2" customWidth="1"/>
@@ -734,12 +648,7 @@
     <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:32">
-      <c r="A3" s="2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="2:32">
       <c r="Y14" s="11">
         <f>B15</f>
         <v>0</v>
@@ -773,7 +682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="2:32">
       <c r="B15" s="1">
         <v>0</v>
       </c>
@@ -812,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="2:32">
       <c r="U16" s="5">
         <f>IF(OR(B15,O26),1,0)</f>
         <v>1</v>
@@ -987,13 +896,13 @@
     </row>
     <row r="89" spans="23:23">
       <c r="W89" s="8">
-        <f>IF(OR(F15,K15,L15,P28),1,0)</f>
+        <f>IF(OR(D15,K15,O26,P28),1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="23:23">
       <c r="W90" s="8">
-        <f>IF(OR(F15,G15,L15,P28),1,0)</f>
+        <f>IF(OR(F15,K15,L15,P28),1,0)</f>
         <v>1</v>
       </c>
     </row>

--- a/3курс/Лабораторные/Архитектура ЭВМ/1/сдвигатель_полная схема.xlsx
+++ b/3курс/Лабораторные/Архитектура ЭВМ/1/сдвигатель_полная схема.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repos\Облако\ВУЗ\3курс\Лабораторные\Архитектура ЭВМ\1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Vyz\3курс\Лабораторные\Архитектура ЭВМ\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41712FA-081E-448A-9E00-7CA7963176EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C419E9-404E-4EEF-85E0-57144BEAB606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B04BFBAC-6633-47BD-86B3-35EFB2D27481}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B04BFBAC-6633-47BD-86B3-35EFB2D27481}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -223,13 +223,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>889426</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>138576</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>245901</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>146</xdr:row>
       <xdr:rowOff>151225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -245,8 +245,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="889426" y="2689619"/>
-          <a:ext cx="13801345" cy="27949889"/>
+          <a:off x="889426" y="2592216"/>
+          <a:ext cx="13750655" cy="27025549"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -613,412 +613,412 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD3A7FC-84A9-4A37-90EA-31D16F697D22}">
-  <dimension ref="B14:AF143"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B2:AF131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2" style="2" customWidth="1"/>
     <col min="2" max="2" width="4" style="2" customWidth="1"/>
-    <col min="3" max="3" width="4.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="4.09765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.59765625" style="2" customWidth="1"/>
     <col min="7" max="7" width="4.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="4.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="4.25" style="2" customWidth="1"/>
-    <col min="13" max="13" width="4.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.3984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.69921875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="4.19921875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="4.59765625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="4.19921875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="4.09765625" style="2" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" customWidth="1"/>
-    <col min="15" max="16" width="4.625" style="2" customWidth="1"/>
+    <col min="15" max="16" width="4.59765625" style="2" customWidth="1"/>
     <col min="17" max="19" width="9" style="2"/>
     <col min="20" max="20" width="7" style="2" customWidth="1"/>
     <col min="21" max="21" width="9" style="2" customWidth="1"/>
-    <col min="22" max="22" width="11.625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="11.59765625" style="2" customWidth="1"/>
     <col min="23" max="23" width="4.5" style="2" customWidth="1"/>
     <col min="24" max="24" width="15.5" style="2" customWidth="1"/>
-    <col min="25" max="25" width="3.875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="4.625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="3.8984375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="4.59765625" style="2" customWidth="1"/>
     <col min="27" max="27" width="4.5" style="2" customWidth="1"/>
-    <col min="28" max="28" width="4.375" style="2" customWidth="1"/>
-    <col min="29" max="29" width="4.625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="4.375" style="2" customWidth="1"/>
-    <col min="31" max="31" width="4.625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="4.875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="4.3984375" style="2" customWidth="1"/>
+    <col min="29" max="29" width="4.59765625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="4.3984375" style="2" customWidth="1"/>
+    <col min="31" max="31" width="4.59765625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="4.8984375" style="2" customWidth="1"/>
     <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="14" spans="2:32">
-      <c r="Y14" s="11">
-        <f>B15</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="11">
-        <f>W28</f>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="11">
-        <f>W41</f>
-        <v>0</v>
-      </c>
-      <c r="AB14" s="11">
-        <f>W54</f>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="11">
-        <f>W70</f>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="11">
-        <f>W94</f>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="11">
-        <f>W119</f>
-        <v>0</v>
-      </c>
-      <c r="AF14" s="11">
-        <f>W143</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:32">
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5">
-        <f>IF(OR(B15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:32">
-      <c r="U16" s="5">
-        <f>IF(OR(B15,O26),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="14:23">
-      <c r="U17" s="5">
-        <f>IF(OR(B15,N23),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="14:23">
-      <c r="U18" s="5">
-        <f>IF(OR(C15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="14:23" ht="12" customHeight="1"/>
-    <row r="22" spans="14:23" ht="3.75" customHeight="1"/>
-    <row r="23" spans="14:23" ht="30.75" customHeight="1">
-      <c r="N23" s="4">
-        <f>IF(NOT(K15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="14:23" ht="1.5" customHeight="1"/>
-    <row r="25" spans="14:23" ht="6" customHeight="1"/>
-    <row r="26" spans="14:23" ht="33" customHeight="1">
-      <c r="O26" s="4">
-        <f>IF(NOT(L15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="14:23" ht="9.75" customHeight="1"/>
-    <row r="28" spans="14:23" ht="28.5" customHeight="1">
-      <c r="P28" s="4">
-        <f>IF(NOT(M15),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="W28" s="5">
-        <f>IF(AND(U15,U16,U17,U18),1,0)</f>
+    <row r="2" spans="2:32">
+      <c r="Y2" s="11">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="11">
+        <f>W16</f>
+        <v>0</v>
+      </c>
+      <c r="AA2" s="11">
+        <f>W29</f>
+        <v>0</v>
+      </c>
+      <c r="AB2" s="11">
+        <f>W42</f>
+        <v>0</v>
+      </c>
+      <c r="AC2" s="11">
+        <f>W58</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="11">
+        <f>W82</f>
+        <v>1</v>
+      </c>
+      <c r="AE2" s="11">
+        <f>W107</f>
+        <v>1</v>
+      </c>
+      <c r="AF2" s="11">
+        <f>W131</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <f>IF(OR(B3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32">
+      <c r="U4" s="5">
+        <f>IF(OR(B3,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32">
+      <c r="U5" s="5">
+        <f>IF(OR(B3,N11),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32">
+      <c r="U6" s="5">
+        <f>IF(OR(C3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32" ht="12" customHeight="1"/>
+    <row r="10" spans="2:32" ht="3.6" customHeight="1"/>
+    <row r="11" spans="2:32" ht="30.6" customHeight="1">
+      <c r="N11" s="4">
+        <f>IF(NOT(K3),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:32" ht="1.5" customHeight="1"/>
+    <row r="13" spans="2:32" ht="6" customHeight="1"/>
+    <row r="14" spans="2:32" ht="33" customHeight="1">
+      <c r="O14" s="4">
+        <f>IF(NOT(L3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32" ht="9.75" customHeight="1"/>
+    <row r="16" spans="2:32" ht="28.5" customHeight="1">
+      <c r="P16" s="4">
+        <f>IF(NOT(M3),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W16" s="5">
+        <f>IF(AND(U3,U4,U5,U6),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="23:23">
+      <c r="W24" s="6">
+        <f>IF(OR(B3,N11),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="23:23">
+      <c r="W25" s="6">
+        <f>IF(OR(B3,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="23:23">
+      <c r="W26" s="6">
+        <f>IF(OR(C3,K3,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="23:23">
+      <c r="W27" s="6">
+        <f>IF(OR(D3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="23:23" ht="10.5" customHeight="1"/>
+    <row r="29" spans="23:23" ht="36.75" customHeight="1">
+      <c r="W29" s="6">
+        <f>IF(AND(W24,W25,W26,W27),1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="23:23">
-      <c r="W36" s="6">
-        <f>IF(OR(B15,N23),1,0)</f>
-        <v>1</v>
+      <c r="W36" s="4">
+        <f>IF(OR(B3,N11),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="23:23">
-      <c r="W37" s="6">
-        <f>IF(OR(B15,O26),1,0)</f>
+      <c r="W37" s="4">
+        <f>IF(OR(B3,N11,P16),1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="23:23">
-      <c r="W38" s="6">
-        <f>IF(OR(C15,K15,L15,P28),1,0)</f>
+      <c r="W38" s="4">
+        <f>IF(OR(D3,K3,L3,,P16),1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="23:23">
-      <c r="W39" s="6">
-        <f>IF(OR(D15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="23:23" ht="10.5" customHeight="1"/>
-    <row r="41" spans="23:23" ht="36.75" customHeight="1">
-      <c r="W41" s="6">
-        <f>IF(AND(W36,W37,W38,W39),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="23:23">
-      <c r="W48" s="4">
-        <f>IF(OR(B15,N23),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="23:23">
-      <c r="W49" s="4">
-        <f>IF(OR(B15,N23,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="23:23">
-      <c r="W50" s="4">
-        <f>IF(OR(D15,K15,L15,,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="23:23">
-      <c r="W51" s="4">
-        <f>IF(OR(C15,K15,M15,O26),1,0)</f>
-        <v>1</v>
+      <c r="W39" s="4">
+        <f>IF(OR(C3,K3,M3,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="23:23">
+      <c r="W40" s="4">
+        <f>IF(OR(E3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="23:23" ht="38.25" customHeight="1">
+      <c r="W42" s="4">
+        <f>IF(AND(W36,W37,W38,W39,W40),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="23:23">
-      <c r="W52" s="4">
-        <f>IF(OR(E15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="23:23" ht="38.25" customHeight="1">
-      <c r="W54" s="4">
-        <f>IF(AND(W48,W49,W50,W51,W52),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="23:23">
-      <c r="W64" s="7">
-        <f>IF(OR(B15,N23),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="23:23">
-      <c r="W65" s="7">
-        <f>IF(OR(F15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="23:23">
-      <c r="W66" s="7">
-        <f>IF(OR(C15,K15,O26,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="23:23">
-      <c r="W67" s="7">
-        <f>IF(OR(E15,K15,L15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="23:23">
-      <c r="W68" s="7">
-        <f>IF(OR(D15,K15,O26,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="23:23" ht="24" customHeight="1"/>
-    <row r="70" spans="23:23" ht="32.25" customHeight="1">
-      <c r="W70" s="7">
-        <f>IF(AND(W64,W65,W66,W67,W68),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="23:23">
-      <c r="W85" s="8">
-        <f>IF(OR(B15,N23,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="23:23">
-      <c r="W86" s="8">
-        <f>IF(OR(B15,N23,O26),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="23:23">
-      <c r="W87" s="8">
-        <f>IF(OR(G15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="23:23">
-      <c r="W88" s="8">
-        <f>IF(OR(C15,N23,L15,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="23:23">
-      <c r="W89" s="8">
-        <f>IF(OR(D15,K15,O26,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="23:23">
-      <c r="W90" s="8">
-        <f>IF(OR(F15,K15,L15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="23:23">
-      <c r="W91" s="8">
-        <f>IF(OR(E15,K15,O26,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="23:23" ht="32.25" customHeight="1">
-      <c r="W94" s="8">
-        <f>IF(AND(W85,W86,W87,W88,W89,W90,W91),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="23:23">
-      <c r="W110" s="9">
-        <f>IF(OR(B15,N23,O26),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="23:23">
-      <c r="W111" s="9">
-        <f>IF(OR(H15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="23:23">
-      <c r="W112" s="9">
-        <f>IF(OR(G15,K15,L15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="23:23">
-      <c r="W113" s="9">
-        <f>IF(OR(E15,K15,O26,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="23:23">
-      <c r="W114" s="9">
-        <f>IF(OR(F15,K15,M15,O26),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="23:23">
-      <c r="W115" s="9">
-        <f>IF(OR(C15,N23,L15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="23:23">
-      <c r="W116" s="9">
-        <f>IF(OR(D15,N23,L15,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="23:23" ht="29.25" customHeight="1">
-      <c r="W119" s="9">
-        <f>IF(AND(W110,W111,W112,W113,W114,W115,W116),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="23:23">
-      <c r="W133" s="10">
-        <f>IF(OR(I15,K15,L15,M15),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="23:23">
-      <c r="W134" s="10">
-        <f>IF(OR(H15,K15,P28,L15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="23:23">
-      <c r="W135" s="10">
-        <f>IF(OR(G15,K15,M15,O26),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="23:23">
-      <c r="W136" s="10">
-        <f>IF(OR(E15,N23,L15,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="23:23">
-      <c r="W137" s="10">
-        <f>IF(OR(B15,N23,O26,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="23:23">
-      <c r="W138" s="10">
-        <f>IF(OR(F15,K15,O26,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="23:23">
-      <c r="W139" s="10">
-        <f>IF(OR(D15,N23,L15,P28),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="23:23">
-      <c r="W140" s="10">
-        <f>IF(OR(C15,N23,O26,M15),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="23:23" ht="21" customHeight="1"/>
-    <row r="143" spans="23:23" ht="28.5" customHeight="1">
-      <c r="W143" s="10">
-        <f>IF(AND(W133,W134,W136,W135,W137,W138,W140,W139),1,0)</f>
-        <v>0</v>
+      <c r="W52" s="7">
+        <f>IF(OR(B3,N11),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="23:23">
+      <c r="W53" s="7">
+        <f>IF(OR(F3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="23:23">
+      <c r="W54" s="7">
+        <f>IF(OR(C3,K3,O14,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="23:23">
+      <c r="W55" s="7">
+        <f>IF(OR(E3,K3,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="23:23">
+      <c r="W56" s="7">
+        <f>IF(OR(D3,K3,O14,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="23:23" ht="24" customHeight="1"/>
+    <row r="58" spans="23:23" ht="32.25" customHeight="1">
+      <c r="W58" s="7">
+        <f>IF(AND(W52,W53,W54,W55,W56),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="23:23">
+      <c r="W73" s="8">
+        <f>IF(OR(B3,N11,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="23:23">
+      <c r="W74" s="8">
+        <f>IF(OR(B3,N11,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="23:23">
+      <c r="W75" s="8">
+        <f>IF(OR(G3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="23:23">
+      <c r="W76" s="8">
+        <f>IF(OR(C3,N11,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="23:23">
+      <c r="W77" s="8">
+        <f>IF(OR(D3,K3,O14,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="23:23">
+      <c r="W78" s="8">
+        <f>IF(OR(F3,K3,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="23:23">
+      <c r="W79" s="8">
+        <f>IF(OR(E3,K3,O14,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="23:23" ht="32.25" customHeight="1">
+      <c r="W82" s="8">
+        <f>IF(AND(W73,W74,W75,W76,W77,W78,W79),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="23:23">
+      <c r="W98" s="9">
+        <f>IF(OR(B3,N11,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="23:23">
+      <c r="W99" s="9">
+        <f>IF(OR(H3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="23:23">
+      <c r="W100" s="9">
+        <f>IF(OR(G3,K3,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="23:23">
+      <c r="W101" s="9">
+        <f>IF(OR(E3,K3,O14,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="23:23">
+      <c r="W102" s="9">
+        <f>IF(OR(F3,K3,M3,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="23:23">
+      <c r="W103" s="9">
+        <f>IF(OR(C3,N11,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="23:23">
+      <c r="W104" s="9">
+        <f>IF(OR(D3,N11,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="23:23" ht="29.25" customHeight="1">
+      <c r="W107" s="9">
+        <f>IF(AND(W98,W99,W100,W101,W102,W103,W104),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="23:23">
+      <c r="W121" s="10">
+        <f>IF(OR(I3,K3,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="23:23">
+      <c r="W122" s="10">
+        <f>IF(OR(H3,K3,P16,L3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="23:23">
+      <c r="W123" s="10">
+        <f>IF(OR(G3,K3,M3,O14),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="23:23">
+      <c r="W124" s="10">
+        <f>IF(OR(E3,N11,L3,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="23:23">
+      <c r="W125" s="10">
+        <f>IF(OR(B3,N11,O14,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="23:23">
+      <c r="W126" s="10">
+        <f>IF(OR(F3,K3,O14,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="23:23">
+      <c r="W127" s="10">
+        <f>IF(OR(D3,N11,L3,P16),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="23:23">
+      <c r="W128" s="10">
+        <f>IF(OR(C3,N11,O14,M3),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="23:23" ht="21" customHeight="1"/>
+    <row r="131" spans="23:23" ht="28.5" customHeight="1">
+      <c r="W131" s="10">
+        <f>IF(AND(W121,W122,W124,W123,W125,W126,W128,W127),1,0)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
